--- a/.claude/docs/Example橋脚4/export/0612_線路方向基礎.xlsx
+++ b/.claude/docs/Example橋脚4/export/0612_線路方向基礎.xlsx
@@ -1765,19 +1765,19 @@
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
       <c r="S50" s="16">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T50" s="11"/>
       <c r="U50" s="11"/>
       <c r="V50" s="11"/>
       <c r="W50" s="16">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="X50" s="11"/>
       <c r="Y50" s="11"/>
       <c r="Z50" s="11"/>
       <c r="AA50" s="16">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AB50" s="11"/>
       <c r="AC50" s="11"/>
@@ -1847,13 +1847,13 @@
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
       <c r="S52" s="13">
-        <v>88.1</v>
+        <v>98</v>
       </c>
       <c r="T52" s="11"/>
       <c r="U52" s="11"/>
       <c r="V52" s="11"/>
       <c r="W52" s="13">
-        <v>75.4</v>
+        <v>88.5</v>
       </c>
       <c r="X52" s="11"/>
       <c r="Y52" s="11"/>
@@ -1880,13 +1880,13 @@
       <c r="Q53" s="11"/>
       <c r="R53" s="11"/>
       <c r="S53" s="13">
-        <v>4089.1</v>
+        <v>3179.5</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
       <c r="V53" s="11"/>
       <c r="W53" s="13">
-        <v>2829</v>
+        <v>1741.9</v>
       </c>
       <c r="X53" s="11"/>
       <c r="Y53" s="11"/>
@@ -1913,13 +1913,13 @@
       <c r="Q54" s="11"/>
       <c r="R54" s="11"/>
       <c r="S54" s="13">
-        <v>18.5</v>
+        <v>21.7</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
       <c r="W54" s="13">
-        <v>21.5</v>
+        <v>24</v>
       </c>
       <c r="X54" s="11"/>
       <c r="Y54" s="11"/>
@@ -1987,13 +1987,13 @@
       <c r="Q56" s="11"/>
       <c r="R56" s="11"/>
       <c r="S56" s="17">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
       <c r="T56" s="11"/>
       <c r="U56" s="11"/>
       <c r="V56" s="11"/>
       <c r="W56" s="17">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="X56" s="11"/>
       <c r="Y56" s="11"/>
@@ -2053,13 +2053,13 @@
       <c r="Q58" s="11"/>
       <c r="R58" s="11"/>
       <c r="S58" s="17">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="T58" s="11"/>
       <c r="U58" s="11"/>
       <c r="V58" s="11"/>
       <c r="W58" s="17">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="X58" s="11"/>
       <c r="Y58" s="11"/>
@@ -2206,19 +2206,19 @@
       <c r="Q63" s="11"/>
       <c r="R63" s="11"/>
       <c r="S63" s="16">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T63" s="11"/>
       <c r="U63" s="11"/>
       <c r="V63" s="11"/>
       <c r="W63" s="16">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X63" s="11"/>
       <c r="Y63" s="11"/>
       <c r="Z63" s="11"/>
       <c r="AA63" s="16">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AB63" s="11"/>
       <c r="AC63" s="11"/>
@@ -2288,13 +2288,13 @@
       <c r="Q65" s="11"/>
       <c r="R65" s="11"/>
       <c r="S65" s="13">
-        <v>88.3</v>
+        <v>98.2</v>
       </c>
       <c r="T65" s="11"/>
       <c r="U65" s="11"/>
       <c r="V65" s="11"/>
       <c r="W65" s="13">
-        <v>75.2</v>
+        <v>88.3</v>
       </c>
       <c r="X65" s="11"/>
       <c r="Y65" s="11"/>
@@ -2321,13 +2321,13 @@
       <c r="Q66" s="11"/>
       <c r="R66" s="11"/>
       <c r="S66" s="13">
-        <v>2704</v>
+        <v>1882.9</v>
       </c>
       <c r="T66" s="11"/>
       <c r="U66" s="11"/>
       <c r="V66" s="11"/>
       <c r="W66" s="13">
-        <v>3964.1</v>
+        <v>3320.4</v>
       </c>
       <c r="X66" s="11"/>
       <c r="Y66" s="11"/>
@@ -2354,13 +2354,13 @@
       <c r="Q67" s="11"/>
       <c r="R67" s="11"/>
       <c r="S67" s="13">
-        <v>18.4</v>
+        <v>21.7</v>
       </c>
       <c r="T67" s="11"/>
       <c r="U67" s="11"/>
       <c r="V67" s="11"/>
       <c r="W67" s="13">
-        <v>21.6</v>
+        <v>24.1</v>
       </c>
       <c r="X67" s="11"/>
       <c r="Y67" s="11"/>
@@ -2428,13 +2428,13 @@
       <c r="Q69" s="11"/>
       <c r="R69" s="11"/>
       <c r="S69" s="17">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="T69" s="11"/>
       <c r="U69" s="11"/>
       <c r="V69" s="11"/>
       <c r="W69" s="17">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="X69" s="11"/>
       <c r="Y69" s="11"/>
@@ -2494,13 +2494,13 @@
       <c r="Q71" s="11"/>
       <c r="R71" s="11"/>
       <c r="S71" s="17">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="T71" s="11"/>
       <c r="U71" s="11"/>
       <c r="V71" s="11"/>
       <c r="W71" s="17">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="X71" s="11"/>
       <c r="Y71" s="11"/>
@@ -2670,7 +2670,7 @@
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
       <c r="I84" s="13">
-        <v>183.7</v>
+        <v>205.3</v>
       </c>
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
@@ -2678,7 +2678,7 @@
       <c r="M84" s="11"/>
       <c r="N84" s="11"/>
       <c r="O84" s="13">
-        <v>4197.4</v>
+        <v>3519</v>
       </c>
       <c r="P84" s="11"/>
       <c r="Q84" s="11"/>
@@ -2686,7 +2686,7 @@
       <c r="S84" s="11"/>
       <c r="T84" s="11"/>
       <c r="U84" s="16">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="V84" s="11"/>
       <c r="W84" s="11"/>
@@ -2711,7 +2711,7 @@
       <c r="G85" s="11"/>
       <c r="H85" s="11"/>
       <c r="I85" s="13">
-        <v>183</v>
+        <v>204.8</v>
       </c>
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
@@ -2719,7 +2719,7 @@
       <c r="M85" s="11"/>
       <c r="N85" s="11"/>
       <c r="O85" s="13">
-        <v>2972.6</v>
+        <v>1823.1</v>
       </c>
       <c r="P85" s="11"/>
       <c r="Q85" s="11"/>
@@ -2727,7 +2727,7 @@
       <c r="S85" s="11"/>
       <c r="T85" s="11"/>
       <c r="U85" s="16">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V85" s="11"/>
       <c r="W85" s="11"/>
@@ -3414,13 +3414,13 @@
       <c r="Q122" s="11"/>
       <c r="R122" s="11"/>
       <c r="S122" s="13">
-        <v>183.7</v>
+        <v>205.3</v>
       </c>
       <c r="T122" s="11"/>
       <c r="U122" s="11"/>
       <c r="V122" s="11"/>
       <c r="W122" s="13">
-        <v>183</v>
+        <v>204.8</v>
       </c>
       <c r="X122" s="11"/>
       <c r="Y122" s="11"/>
@@ -3450,13 +3450,13 @@
       <c r="Q123" s="11"/>
       <c r="R123" s="11"/>
       <c r="S123" s="13">
-        <v>4197.4</v>
+        <v>3519</v>
       </c>
       <c r="T123" s="11"/>
       <c r="U123" s="11"/>
       <c r="V123" s="11"/>
       <c r="W123" s="13">
-        <v>2972.6</v>
+        <v>1823.1</v>
       </c>
       <c r="X123" s="11"/>
       <c r="Y123" s="11"/>
@@ -3486,13 +3486,13 @@
       <c r="Q124" s="11"/>
       <c r="R124" s="11"/>
       <c r="S124" s="13">
-        <v>3011.7</v>
+        <v>2902.9</v>
       </c>
       <c r="T124" s="11"/>
       <c r="U124" s="11"/>
       <c r="V124" s="11"/>
       <c r="W124" s="13">
-        <v>2800.1</v>
+        <v>2558.3</v>
       </c>
       <c r="X124" s="11"/>
       <c r="Y124" s="11"/>
@@ -3522,13 +3522,13 @@
       <c r="Q125" s="11"/>
       <c r="R125" s="11"/>
       <c r="S125" s="17">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="T125" s="11"/>
       <c r="U125" s="11"/>
       <c r="V125" s="11"/>
       <c r="W125" s="17">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="X125" s="11"/>
       <c r="Y125" s="11"/>
@@ -3831,19 +3831,19 @@
       <c r="Q158" s="11"/>
       <c r="R158" s="11"/>
       <c r="S158" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T158" s="11"/>
       <c r="U158" s="11"/>
       <c r="V158" s="11"/>
       <c r="W158" s="16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X158" s="11"/>
       <c r="Y158" s="11"/>
       <c r="Z158" s="11"/>
       <c r="AA158" s="16">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AB158" s="11"/>
       <c r="AC158" s="11"/>
@@ -3899,19 +3899,19 @@
       <c r="Q160" s="11"/>
       <c r="R160" s="11"/>
       <c r="S160" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T160" s="11"/>
       <c r="U160" s="11"/>
       <c r="V160" s="11"/>
       <c r="W160" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X160" s="11"/>
       <c r="Y160" s="11"/>
       <c r="Z160" s="11"/>
       <c r="AA160" s="16">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AB160" s="11"/>
       <c r="AC160" s="11"/>
@@ -3933,19 +3933,19 @@
       <c r="Q161" s="11"/>
       <c r="R161" s="11"/>
       <c r="S161" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T161" s="11"/>
       <c r="U161" s="11"/>
       <c r="V161" s="11"/>
       <c r="W161" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X161" s="11"/>
       <c r="Y161" s="11"/>
       <c r="Z161" s="11"/>
       <c r="AA161" s="16">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AB161" s="11"/>
       <c r="AC161" s="11"/>
@@ -4021,7 +4021,7 @@
       <c r="U163" s="11"/>
       <c r="V163" s="11"/>
       <c r="W163" s="13">
-        <v>2503.4</v>
+        <v>3030.9</v>
       </c>
       <c r="X163" s="11"/>
       <c r="Y163" s="11"/>
@@ -4089,13 +4089,13 @@
       <c r="U165" s="11"/>
       <c r="V165" s="11"/>
       <c r="W165" s="27">
-        <v>0.263</v>
+        <v>4.284</v>
       </c>
       <c r="X165" s="11"/>
       <c r="Y165" s="11"/>
       <c r="Z165" s="11"/>
       <c r="AA165" s="27">
-        <v>6.403</v>
+        <v>7.175</v>
       </c>
       <c r="AB165" s="11"/>
       <c r="AC165" s="11"/>
@@ -4123,13 +4123,13 @@
       <c r="U166" s="11"/>
       <c r="V166" s="11"/>
       <c r="W166" s="14">
-        <v>6e-05</v>
+        <v>0.00043</v>
       </c>
       <c r="X166" s="11"/>
       <c r="Y166" s="11"/>
       <c r="Z166" s="11"/>
       <c r="AA166" s="14">
-        <v>0.00071</v>
+        <v>0.00078</v>
       </c>
       <c r="AB166" s="11"/>
       <c r="AC166" s="11"/>
@@ -4457,7 +4457,7 @@
       <c r="U175" s="11"/>
       <c r="V175" s="11"/>
       <c r="W175" s="17">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="X175" s="11"/>
       <c r="Y175" s="11"/>
@@ -4525,13 +4525,13 @@
       <c r="U177" s="11"/>
       <c r="V177" s="11"/>
       <c r="W177" s="17">
-        <v>0.03</v>
+        <v>0.44</v>
       </c>
       <c r="X177" s="11"/>
       <c r="Y177" s="11"/>
       <c r="Z177" s="11"/>
       <c r="AA177" s="17">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="AB177" s="11"/>
       <c r="AC177" s="11"/>
@@ -4559,13 +4559,13 @@
       <c r="U178" s="11"/>
       <c r="V178" s="11"/>
       <c r="W178" s="17">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="X178" s="11"/>
       <c r="Y178" s="11"/>
       <c r="Z178" s="11"/>
       <c r="AA178" s="17">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AB178" s="11"/>
       <c r="AC178" s="11"/>
